--- a/taxas_bancos.xlsx
+++ b/taxas_bancos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C0568A-7EB9-43C9-B798-13D75A23D0B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89465FBD-A23C-4F50-ABC1-DBD175FD3D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11172" yWindow="5520" windowWidth="34560" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26736" yWindow="5568" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>BCO MERCEDES-BENZ S.A.</t>
   </si>
@@ -87,9 +87,6 @@
     <t>SINOSSERRA S/A - SCFI</t>
   </si>
   <si>
-    <t>BANCO MONEO S.A.</t>
-  </si>
-  <si>
     <t>SANTANDER SCFI S.A.</t>
   </si>
   <si>
@@ -148,6 +145,15 @@
   </si>
   <si>
     <t>Banco</t>
+  </si>
+  <si>
+    <t>BCO VOLVO BRASIL S.A.</t>
+  </si>
+  <si>
+    <t>AL5 S.A. SCFI</t>
+  </si>
+  <si>
+    <t>BCO DO ESTADO DO RS S.A.</t>
   </si>
 </sst>
 </file>
@@ -465,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" bestFit="1" customWidth="1"/>
@@ -474,322 +480,338 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B2">
-        <v>0.46</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="B3">
-        <v>0.64</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4">
-        <v>0.92</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>1.0900000000000001</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B7">
-        <v>1.19</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>1.45</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B12">
-        <v>1.49</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B13">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B14">
-        <v>1.58</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B15">
-        <v>1.63</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B16">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B18">
-        <v>1.72</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B19">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B20">
-        <v>1.75</v>
+        <v>2.2599999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B21">
-        <v>1.8</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B22">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B23">
-        <v>1.81</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B24">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B26">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B27">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B29">
-        <v>1.97</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B30">
-        <v>2.0099999999999998</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B31">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B32">
-        <v>2.25</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B33">
-        <v>2.39</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B34">
-        <v>2.64</v>
+        <v>2.0299999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B35">
-        <v>2.68</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B36">
-        <v>2.93</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B37">
-        <v>3.1</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B38">
-        <v>3.19</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="B39">
-        <v>3.25</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B40">
-        <v>3.32</v>
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/taxas_bancos.xlsx
+++ b/taxas_bancos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89465FBD-A23C-4F50-ABC1-DBD175FD3D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7F852E-5FFF-46B5-832B-DCA3C1FEA919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26736" yWindow="5568" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25656" yWindow="4956" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -491,7 +491,7 @@
         <v>32</v>
       </c>
       <c r="B2">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -507,7 +507,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>1.59</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -515,7 +515,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -523,7 +523,7 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -531,7 +531,7 @@
         <v>33</v>
       </c>
       <c r="B7">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -539,7 +539,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -547,7 +547,7 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -555,7 +555,7 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>1.87</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -563,7 +563,7 @@
         <v>18</v>
       </c>
       <c r="B11">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -571,7 +571,7 @@
         <v>27</v>
       </c>
       <c r="B12">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -579,7 +579,7 @@
         <v>26</v>
       </c>
       <c r="B13">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -595,7 +595,7 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -603,7 +603,7 @@
         <v>22</v>
       </c>
       <c r="B16">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -611,7 +611,7 @@
         <v>14</v>
       </c>
       <c r="B17">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -627,7 +627,7 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -635,7 +635,7 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>2.2599999999999998</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -643,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="B21">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -659,7 +659,7 @@
         <v>3</v>
       </c>
       <c r="B23">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -667,7 +667,7 @@
         <v>17</v>
       </c>
       <c r="B24">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -675,7 +675,7 @@
         <v>21</v>
       </c>
       <c r="B25">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -683,7 +683,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -699,7 +699,7 @@
         <v>29</v>
       </c>
       <c r="B28">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -707,7 +707,7 @@
         <v>31</v>
       </c>
       <c r="B29">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -715,7 +715,7 @@
         <v>2</v>
       </c>
       <c r="B30">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -723,7 +723,7 @@
         <v>13</v>
       </c>
       <c r="B31">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -731,7 +731,7 @@
         <v>25</v>
       </c>
       <c r="B32">
-        <v>2.2000000000000002</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -739,7 +739,7 @@
         <v>35</v>
       </c>
       <c r="B33">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
       <c r="B34">
-        <v>2.0299999999999998</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -755,7 +755,7 @@
         <v>37</v>
       </c>
       <c r="B35">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -763,7 +763,7 @@
         <v>12</v>
       </c>
       <c r="B36">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -771,7 +771,7 @@
         <v>15</v>
       </c>
       <c r="B37">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -779,7 +779,7 @@
         <v>20</v>
       </c>
       <c r="B38">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B39">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -795,7 +795,7 @@
         <v>34</v>
       </c>
       <c r="B40">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -803,7 +803,7 @@
         <v>19</v>
       </c>
       <c r="B41">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -811,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="B42">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/taxas_bancos.xlsx
+++ b/taxas_bancos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7F852E-5FFF-46B5-832B-DCA3C1FEA919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A86318-7CB0-4576-BAB7-8EB487D48260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25656" yWindow="4956" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11100" yWindow="4956" windowWidth="33228" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>BCO MERCEDES-BENZ S.A.</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>BCO DO ESTADO DO RS S.A.</t>
+  </si>
+  <si>
+    <t>BANCO MONEO S.A.</t>
   </si>
 </sst>
 </file>
@@ -471,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" bestFit="1" customWidth="1"/>
@@ -491,7 +494,7 @@
         <v>32</v>
       </c>
       <c r="B2">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -507,7 +510,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>0.37</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -515,7 +518,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -523,295 +526,303 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B7">
-        <v>3.06</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="B8">
-        <v>1.56</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
-        <v>2.0699999999999998</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B11">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B14">
-        <v>1.0900000000000001</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B15">
-        <v>3.23</v>
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B16">
-        <v>1.86</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B17">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B18">
-        <v>2.4900000000000002</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="B19">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B20">
-        <v>2.38</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B21">
-        <v>0.82</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B22">
-        <v>1.43</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B23">
-        <v>0.86</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B24">
-        <v>1.73</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B25">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B26">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B27">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B28">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B29">
-        <v>2.67</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="B30">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B31">
-        <v>1.63</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B32">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B33">
-        <v>3.03</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B34">
-        <v>2.0699999999999998</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B35">
-        <v>3.47</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="B36">
-        <v>1.61</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B37">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B38">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B39">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B40">
-        <v>3.2</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B41">
-        <v>1.88</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B42">
-        <v>1.51</v>
+      <c r="B43">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/taxas_bancos.xlsx
+++ b/taxas_bancos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A86318-7CB0-4576-BAB7-8EB487D48260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A64FBF-F09F-40F3-8097-0E8A440F07FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11100" yWindow="4956" windowWidth="33228" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12108" yWindow="5592" windowWidth="33228" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -510,7 +510,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>1.47</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -518,7 +518,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -526,7 +526,7 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -534,7 +534,7 @@
         <v>43</v>
       </c>
       <c r="B7">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -542,7 +542,7 @@
         <v>33</v>
       </c>
       <c r="B8">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -550,7 +550,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -558,7 +558,7 @@
         <v>23</v>
       </c>
       <c r="B10">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -574,7 +574,7 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -582,7 +582,7 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -590,7 +590,7 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -598,7 +598,7 @@
         <v>4</v>
       </c>
       <c r="B15">
-        <v>1.1100000000000001</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -606,7 +606,7 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -614,7 +614,7 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -622,7 +622,7 @@
         <v>14</v>
       </c>
       <c r="B18">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -630,7 +630,7 @@
         <v>42</v>
       </c>
       <c r="B19">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -646,7 +646,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>2.29</v>
+        <v>2.4700000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -654,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="B22">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -662,7 +662,7 @@
         <v>6</v>
       </c>
       <c r="B23">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -670,7 +670,7 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -678,7 +678,7 @@
         <v>17</v>
       </c>
       <c r="B25">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -686,7 +686,7 @@
         <v>21</v>
       </c>
       <c r="B26">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -694,7 +694,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -702,7 +702,7 @@
         <v>40</v>
       </c>
       <c r="B28">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -710,7 +710,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>2.31</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -718,7 +718,7 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -726,7 +726,7 @@
         <v>2</v>
       </c>
       <c r="B31">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -742,7 +742,7 @@
         <v>25</v>
       </c>
       <c r="B33">
-        <v>1.89</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -750,7 +750,7 @@
         <v>35</v>
       </c>
       <c r="B34">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -758,7 +758,7 @@
         <v>28</v>
       </c>
       <c r="B35">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -766,7 +766,7 @@
         <v>37</v>
       </c>
       <c r="B36">
-        <v>3.41</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -774,7 +774,7 @@
         <v>12</v>
       </c>
       <c r="B37">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -782,7 +782,7 @@
         <v>15</v>
       </c>
       <c r="B38">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -814,7 +814,7 @@
         <v>19</v>
       </c>
       <c r="B42">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -822,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="B43">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>
